--- a/docs/reference/STEGO-K1_총견적서.xlsx
+++ b/docs/reference/STEGO-K1_총견적서.xlsx
@@ -20,7 +20,7 @@
   <definedNames>
     <definedName name="_xlnm.Print_Area" localSheetId="1">차량견적서!$A$1:$N$33</definedName>
   </definedNames>
-  <calcPr calcId="191028"/>
+  <calcPr calcId="191028" fullCalcOnLoad="1"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -4525,8 +4525,7 @@
       </c>
       <c r="L26" s="11"/>
       <c r="M26" s="12">
-        <f>ROUNDDOWN((D20+I20)/11*10,-1)</f>
-        <v>45070450</v>
+        <f>D20+I20-ROUNDDOWN((D10+D11+D14+I20)/11,-1)</f>
       </c>
     </row>
     <row r="27" spans="1:15" ht="16.5" customHeight="1">
